--- a/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,5</t>
+          <t>-1,57; 3,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,13</t>
+          <t>-1,53; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 12,05</t>
+          <t>2,29; 11,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-99,09; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,57; 1216,93</t>
+          <t>-74,26; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,75; 508,02</t>
+          <t>29,87; 518,93</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,58</t>
+          <t>-1,26; 4,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,57</t>
+          <t>-1,49; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,1</t>
+          <t>-3,5; 5,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 237,95</t>
+          <t>-31,2; 243,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 408,98</t>
+          <t>-65,52; 442,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 94,99</t>
+          <t>-40,13; 102,69</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,33</t>
+          <t>-2,71; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,89</t>
+          <t>-2,55; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 5,01</t>
+          <t>-4,36; 4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,89; 326,62</t>
+          <t>-73,95; 341,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 156,5</t>
+          <t>-60,21; 125,27</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,26</t>
+          <t>-2,76; 4,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,4</t>
+          <t>-6,84; 1,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 2,69</t>
+          <t>-7,45; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 180,02</t>
+          <t>-49,35; 178,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 26,76</t>
+          <t>-66,5; 30,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 32,6</t>
+          <t>-53,42; 40,85</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,22</t>
+          <t>-0,74; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,54</t>
+          <t>-1,76; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,37</t>
+          <t>-1,51; 3,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 98,45</t>
+          <t>-22,76; 108,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 53,53</t>
+          <t>-40,08; 53,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 56,01</t>
+          <t>-20,58; 55,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,45</t>
+          <t>-1,61; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,92</t>
+          <t>-1,27; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,81</t>
+          <t>2,45; 12,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>-95,69; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-74,26; —</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,87; 518,93</t>
+          <t>31,47; 507,36</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,78</t>
+          <t>-1,64; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,86</t>
+          <t>-1,6; 2,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,59</t>
+          <t>-3,74; 5,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 243,31</t>
+          <t>-37,88; 232,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 442,66</t>
+          <t>-67,64; 423,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 102,69</t>
+          <t>-38,79; 97,25</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,65</t>
+          <t>-2,47; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,87</t>
+          <t>-2,32; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 4,12</t>
+          <t>-4,35; 4,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 341,51</t>
+          <t>-71,38; 330,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 125,27</t>
+          <t>-55,85; 141,38</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,39</t>
+          <t>-2,93; 4,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,66</t>
+          <t>-6,64; 1,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 3,16</t>
+          <t>-7,43; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 178,23</t>
+          <t>-51,48; 177,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 30,73</t>
+          <t>-63,27; 30,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 40,85</t>
+          <t>-55,47; 41,26</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,31</t>
+          <t>-0,69; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,55</t>
+          <t>-1,76; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,29</t>
+          <t>-1,32; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 108,39</t>
+          <t>-22,18; 96,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 53,79</t>
+          <t>-38,89; 53,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 55,47</t>
+          <t>-16,81; 54,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Habitat-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>171,88%</t>
+          <t>171,43%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,81</t>
+          <t>-1,53; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,95</t>
+          <t>-1,06; 5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,41</t>
+          <t>2,01; 11,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-95,69; —</t>
+          <t>-99,09; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,57; 1216,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,47; 507,36</t>
+          <t>30,81; 519,63</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,77</t>
+          <t>-1,33; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,8</t>
+          <t>-1,67; 2,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,08</t>
+          <t>-2,41; 6,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 232,36</t>
+          <t>-33,71; 237,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; 423,89</t>
+          <t>-65,99; 408,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 97,25</t>
+          <t>-31,97; 120,38</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -792,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,63</t>
+          <t>-2,37; 1,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,79</t>
+          <t>-2,3; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 4,55</t>
+          <t>-2,94; 6,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -812,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 330,5</t>
+          <t>-72,89; 326,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 141,38</t>
+          <t>-42,68; 207,93</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-2,2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-21,66%</t>
+          <t>-20,61%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,35</t>
+          <t>-2,79; 4,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,69</t>
+          <t>-7,06; 1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 3,24</t>
+          <t>-7,64; 2,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 177,41</t>
+          <t>-48,88; 180,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 30,05</t>
+          <t>-63,81; 26,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 41,26</t>
+          <t>-56,24; 34,68</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,18</t>
+          <t>-0,71; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,44</t>
+          <t>-1,65; 1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,39</t>
+          <t>-0,86; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 96,86</t>
+          <t>-22,07; 98,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 53,49</t>
+          <t>-39,14; 53,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 54,31</t>
+          <t>-11,29; 70,32</t>
         </is>
       </c>
     </row>
